--- a/excel/Batch_18_20_Leads_Tracker.xlsx
+++ b/excel/Batch_18_20_Leads_Tracker.xlsx
@@ -32,10 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd mmm yyyy"/>
-    <numFmt numFmtId="201" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -511,10 +510,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H2" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J2" t="str">
         <v>Re: Website improvement ideas for AK Carpentry</v>
@@ -593,10 +592,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H3" t="str">
-        <v>Draft</v>
+        <v>Mail Not Found</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J3" t="str">
         <v>Re: Website improvement ideas for Deep Clean Carpet &amp; Upholstery Cleaning</v>
@@ -675,10 +674,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J4" t="str">
         <v>Re: Website improvement ideas for Graves &amp; Starey</v>
@@ -757,10 +756,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J5" t="str">
         <v>Re: Website improvement ideas for Restall Seating Systems</v>
@@ -839,10 +838,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J6" t="str">
         <v>Re: Website improvement ideas for Turriff Tackle &amp; Trophies / Fishing the Deveron</v>
@@ -921,10 +920,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J7" t="str">
         <v>Re: Website improvement ideas for Account 4 It</v>
@@ -1003,10 +1002,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J8" t="str">
         <v>Re: Website improvement ideas for Jeffy Salt</v>
@@ -1085,10 +1084,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J9" t="str">
         <v>Re: Website improvement ideas for Carpentry Contractors</v>
@@ -1167,10 +1166,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J10" t="str">
         <v>Re: Website improvement ideas for Ayton Castle</v>
@@ -1249,10 +1248,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J11" t="str">
         <v>Re: Website improvement ideas for Surrey Advanced Control</v>
@@ -1331,10 +1330,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H12" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J12" t="str">
         <v>Re: Website improvement ideas for Eco Energy Controls</v>
@@ -1413,10 +1412,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H13" t="str">
-        <v>Draft</v>
+        <v>Replied</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J13" t="str">
         <v>Re: Website improvement ideas for 7 Star Catering UK</v>
@@ -1495,10 +1494,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J14" t="str">
         <v>Re: Website improvement ideas for Build Projects</v>
@@ -1577,10 +1576,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J15" t="str">
         <v>Re: Website improvement ideas for Time Hairdressing</v>
@@ -1659,10 +1658,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J16" t="str">
         <v>Re: Website improvement ideas for Clifford Glass Studio</v>
@@ -1743,10 +1742,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H17" t="str">
-        <v>Draft</v>
+        <v>Mail Not Found</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J17" t="str">
         <v>Re: Website improvement ideas for Canteen Records</v>
@@ -1825,10 +1824,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J18" t="str">
         <v>Re: Website improvement ideas for Abbey Family History</v>
@@ -1908,10 +1907,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J19" t="str">
         <v>Re: Website improvement ideas for GroundsCare Products</v>
@@ -1990,10 +1989,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>2026-10-05</v>
       </c>
       <c r="J20" t="str">
         <v>Re: Website improvement ideas for Euro Horse Boxes</v>

--- a/excel/Batch_18_20_Leads_Tracker.xlsx
+++ b/excel/Batch_18_20_Leads_Tracker.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -418,6 +418,7 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,9 @@
       </c>
       <c r="R1" t="str">
         <v>Lead Status</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -557,6 +561,9 @@
       <c r="R2" t="str">
         <v/>
       </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -639,6 +646,9 @@
       <c r="R3" t="str">
         <v/>
       </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -721,6 +731,9 @@
       <c r="R4" t="str">
         <v/>
       </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
@@ -803,6 +816,9 @@
       <c r="R5" t="str">
         <v/>
       </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
@@ -885,6 +901,9 @@
       <c r="R6" t="str">
         <v/>
       </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
@@ -967,6 +986,9 @@
       <c r="R7" t="str">
         <v/>
       </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
@@ -1049,6 +1071,9 @@
       <c r="R8" t="str">
         <v/>
       </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
@@ -1131,6 +1156,9 @@
       <c r="R9" t="str">
         <v/>
       </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
@@ -1213,6 +1241,9 @@
       <c r="R10" t="str">
         <v/>
       </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
@@ -1295,6 +1326,9 @@
       <c r="R11" t="str">
         <v/>
       </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
@@ -1377,6 +1411,9 @@
       <c r="R12" t="str">
         <v/>
       </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
@@ -1459,6 +1496,9 @@
       <c r="R13" t="str">
         <v/>
       </c>
+      <c r="S13" t="str">
+        <v>Interested, but, price is high</v>
+      </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
@@ -1541,6 +1581,9 @@
       <c r="R14" t="str">
         <v/>
       </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
@@ -1623,6 +1666,9 @@
       <c r="R15" t="str">
         <v/>
       </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
@@ -1705,6 +1751,9 @@
       <c r="R16" t="str">
         <v/>
       </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
@@ -1789,6 +1838,9 @@
       <c r="R17" t="str">
         <v/>
       </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
@@ -1871,6 +1923,9 @@
       <c r="R18" t="str">
         <v/>
       </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
@@ -1954,6 +2009,9 @@
       <c r="R19" t="str">
         <v/>
       </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
@@ -2036,10 +2094,13 @@
       <c r="R20" t="str">
         <v/>
       </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S20"/>
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
